--- a/regression_deneme/regression_with_nn/konak_monthly_true_and_predicted_test.xlsx
+++ b/regression_deneme/regression_with_nn/konak_monthly_true_and_predicted_test.xlsx
@@ -461,7 +461,7 @@
         <v>240</v>
       </c>
       <c r="D2" t="n">
-        <v>217.4785679121873</v>
+        <v>244.9299588233328</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>197</v>
       </c>
       <c r="D3" t="n">
-        <v>200.6638336271878</v>
+        <v>214.2518373430046</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         <v>166</v>
       </c>
       <c r="D4" t="n">
-        <v>169.7180000407016</v>
+        <v>186.3273963248341</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +503,7 @@
         <v>174</v>
       </c>
       <c r="D5" t="n">
-        <v>178.1946016207943</v>
+        <v>200.4797521130974</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>150</v>
       </c>
       <c r="D6" t="n">
-        <v>148.1564082370685</v>
+        <v>151.3910934730887</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>182</v>
       </c>
       <c r="D7" t="n">
-        <v>186.4527736756399</v>
+        <v>199.7184851613612</v>
       </c>
     </row>
     <row r="8">
@@ -545,7 +545,7 @@
         <v>190</v>
       </c>
       <c r="D8" t="n">
-        <v>181.0772590799944</v>
+        <v>192.781349017642</v>
       </c>
     </row>
   </sheetData>
